--- a/99 - Excels/PointingHours.xlsx
+++ b/99 - Excels/PointingHours.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\99 - Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18DEA0A0-8F9F-47DD-8EE4-65F52A16F164}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B27CB32E-7F00-4F33-AED8-E154544B75CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="247">
   <si>
     <t>LPs</t>
   </si>
@@ -31,100 +31,736 @@
     <t>Status</t>
   </si>
   <si>
-    <t>LP-056898</t>
-  </si>
-  <si>
-    <t>Apointing created!</t>
-  </si>
-  <si>
-    <t>LP-056899</t>
-  </si>
-  <si>
-    <t>LP-056669</t>
-  </si>
-  <si>
-    <t>LP-056900</t>
-  </si>
-  <si>
-    <t>LP-056614</t>
-  </si>
-  <si>
-    <t>LP-057928</t>
-  </si>
-  <si>
-    <t>LP-056668</t>
-  </si>
-  <si>
-    <t>LP-056667</t>
-  </si>
-  <si>
-    <t>LP-056901</t>
-  </si>
-  <si>
-    <t>LP-057037</t>
-  </si>
-  <si>
-    <t>LP-057040</t>
-  </si>
-  <si>
-    <t>LP-057041</t>
-  </si>
-  <si>
-    <t>LP-057042</t>
-  </si>
-  <si>
-    <t>LP-057931</t>
-  </si>
-  <si>
-    <t>LP-057043</t>
-  </si>
-  <si>
-    <t>LP-057048</t>
-  </si>
-  <si>
-    <t>LP-057271</t>
-  </si>
-  <si>
-    <t>LP-057273</t>
-  </si>
-  <si>
-    <t>LP-057337</t>
-  </si>
-  <si>
-    <t>LP-057338</t>
-  </si>
-  <si>
-    <t>LP-057339</t>
-  </si>
-  <si>
-    <t>LP-058836</t>
-  </si>
-  <si>
-    <t>LP-058166</t>
-  </si>
-  <si>
-    <t>LP-058165</t>
-  </si>
-  <si>
-    <t>LP-058265</t>
-  </si>
-  <si>
-    <t>LP-059188</t>
-  </si>
-  <si>
-    <t>LP-059878</t>
-  </si>
-  <si>
-    <t>LP-057371</t>
-  </si>
-  <si>
-    <t>LP-057372</t>
-  </si>
-  <si>
-    <t>LP-057373</t>
-  </si>
-  <si>
-    <t>LP-057374</t>
+    <t>LP-057607</t>
+  </si>
+  <si>
+    <t>LP-057734</t>
+  </si>
+  <si>
+    <t>LP-057735</t>
+  </si>
+  <si>
+    <t>LP-057632</t>
+  </si>
+  <si>
+    <t>LP-057815</t>
+  </si>
+  <si>
+    <t>LP-057661</t>
+  </si>
+  <si>
+    <t>LP-058193</t>
+  </si>
+  <si>
+    <t>LP-057647</t>
+  </si>
+  <si>
+    <t>LP-057669</t>
+  </si>
+  <si>
+    <t>LP-057649</t>
+  </si>
+  <si>
+    <t>LP-057650</t>
+  </si>
+  <si>
+    <t>LP-057651</t>
+  </si>
+  <si>
+    <t>LP-057652</t>
+  </si>
+  <si>
+    <t>LP-057653</t>
+  </si>
+  <si>
+    <t>LP-057635</t>
+  </si>
+  <si>
+    <t>LP-057636</t>
+  </si>
+  <si>
+    <t>LP-057637</t>
+  </si>
+  <si>
+    <t>LP-057639</t>
+  </si>
+  <si>
+    <t>LP-057737</t>
+  </si>
+  <si>
+    <t>LP-057738</t>
+  </si>
+  <si>
+    <t>LP-057743</t>
+  </si>
+  <si>
+    <t>LP-057742</t>
+  </si>
+  <si>
+    <t>LP-057663</t>
+  </si>
+  <si>
+    <t>LP-057667</t>
+  </si>
+  <si>
+    <t>LP-057662</t>
+  </si>
+  <si>
+    <t>LP-057665</t>
+  </si>
+  <si>
+    <t>LP-057666</t>
+  </si>
+  <si>
+    <t>LP-057816</t>
+  </si>
+  <si>
+    <t>LP-057682</t>
+  </si>
+  <si>
+    <t>LP-057680</t>
+  </si>
+  <si>
+    <t>LP-057681</t>
+  </si>
+  <si>
+    <t>LP-057693</t>
+  </si>
+  <si>
+    <t>LP-057677</t>
+  </si>
+  <si>
+    <t>LP-057750</t>
+  </si>
+  <si>
+    <t>LP-057748</t>
+  </si>
+  <si>
+    <t>LP-057819</t>
+  </si>
+  <si>
+    <t>LP-057846</t>
+  </si>
+  <si>
+    <t>LP-057820</t>
+  </si>
+  <si>
+    <t>LP-057845</t>
+  </si>
+  <si>
+    <t>LP-057907</t>
+  </si>
+  <si>
+    <t>LP-057747</t>
+  </si>
+  <si>
+    <t>LP-057772</t>
+  </si>
+  <si>
+    <t>LP-058200</t>
+  </si>
+  <si>
+    <t>LP-057897</t>
+  </si>
+  <si>
+    <t>LP-057810</t>
+  </si>
+  <si>
+    <t>LP-057809</t>
+  </si>
+  <si>
+    <t>LP-057808</t>
+  </si>
+  <si>
+    <t>LP-057811</t>
+  </si>
+  <si>
+    <t>LP-057812</t>
+  </si>
+  <si>
+    <t>LP-057817</t>
+  </si>
+  <si>
+    <t>LP-057769</t>
+  </si>
+  <si>
+    <t>LP-057751</t>
+  </si>
+  <si>
+    <t>LP-057899</t>
+  </si>
+  <si>
+    <t>LP-057898</t>
+  </si>
+  <si>
+    <t>LP-057770</t>
+  </si>
+  <si>
+    <t>LP-057806</t>
+  </si>
+  <si>
+    <t>LP-057771</t>
+  </si>
+  <si>
+    <t>LP-057805</t>
+  </si>
+  <si>
+    <t>LP-057807</t>
+  </si>
+  <si>
+    <t>LP-057814</t>
+  </si>
+  <si>
+    <t>LP-057906</t>
+  </si>
+  <si>
+    <t>LP-057901</t>
+  </si>
+  <si>
+    <t>LP-057904</t>
+  </si>
+  <si>
+    <t>LP-057905</t>
+  </si>
+  <si>
+    <t>LP-057903</t>
+  </si>
+  <si>
+    <t>LP-057900</t>
+  </si>
+  <si>
+    <t>LP-057813</t>
+  </si>
+  <si>
+    <t>LP-057902</t>
+  </si>
+  <si>
+    <t>LP-058036</t>
+  </si>
+  <si>
+    <t>LP-057908</t>
+  </si>
+  <si>
+    <t>LP-057842</t>
+  </si>
+  <si>
+    <t>LP-057694</t>
+  </si>
+  <si>
+    <t>LP-057695</t>
+  </si>
+  <si>
+    <t>LP-057696</t>
+  </si>
+  <si>
+    <t>LP-058037</t>
+  </si>
+  <si>
+    <t>LP-058038</t>
+  </si>
+  <si>
+    <t>LP-057912</t>
+  </si>
+  <si>
+    <t>LP-057911</t>
+  </si>
+  <si>
+    <t>LP-058040</t>
+  </si>
+  <si>
+    <t>LP-058039</t>
+  </si>
+  <si>
+    <t>LP-057917</t>
+  </si>
+  <si>
+    <t>LP-057916</t>
+  </si>
+  <si>
+    <t>LP-058195</t>
+  </si>
+  <si>
+    <t>LP-058144</t>
+  </si>
+  <si>
+    <t>LP-058137</t>
+  </si>
+  <si>
+    <t>LP-058201</t>
+  </si>
+  <si>
+    <t>LP-058141</t>
+  </si>
+  <si>
+    <t>LP-058140</t>
+  </si>
+  <si>
+    <t>LP-058139</t>
+  </si>
+  <si>
+    <t>LP-058142</t>
+  </si>
+  <si>
+    <t>LP-058194</t>
+  </si>
+  <si>
+    <t>LP-058030</t>
+  </si>
+  <si>
+    <t>LP-058281</t>
+  </si>
+  <si>
+    <t>LP-058100</t>
+  </si>
+  <si>
+    <t>LP-057923</t>
+  </si>
+  <si>
+    <t>LP-058104</t>
+  </si>
+  <si>
+    <t>LP-058107</t>
+  </si>
+  <si>
+    <t>LP-058109</t>
+  </si>
+  <si>
+    <t>LP-058111</t>
+  </si>
+  <si>
+    <t>LP-058101</t>
+  </si>
+  <si>
+    <t>LP-058102</t>
+  </si>
+  <si>
+    <t>LP-058117</t>
+  </si>
+  <si>
+    <t>LP-058099</t>
+  </si>
+  <si>
+    <t>LP-058766</t>
+  </si>
+  <si>
+    <t>LP-058308</t>
+  </si>
+  <si>
+    <t>LP-058305</t>
+  </si>
+  <si>
+    <t>LP-058303</t>
+  </si>
+  <si>
+    <t>LP-058031</t>
+  </si>
+  <si>
+    <t>LP-058032</t>
+  </si>
+  <si>
+    <t>LP-058560</t>
+  </si>
+  <si>
+    <t>LP-058035</t>
+  </si>
+  <si>
+    <t>LP-058034</t>
+  </si>
+  <si>
+    <t>LP-058042</t>
+  </si>
+  <si>
+    <t>LP-058025</t>
+  </si>
+  <si>
+    <t>LP-058024</t>
+  </si>
+  <si>
+    <t>LP-058116</t>
+  </si>
+  <si>
+    <t>LP-058118</t>
+  </si>
+  <si>
+    <t>LP-058120</t>
+  </si>
+  <si>
+    <t>LP-058350</t>
+  </si>
+  <si>
+    <t>LP-058351</t>
+  </si>
+  <si>
+    <t>LP-058352</t>
+  </si>
+  <si>
+    <t>LP-058353</t>
+  </si>
+  <si>
+    <t>LP-058121</t>
+  </si>
+  <si>
+    <t>LP-058122</t>
+  </si>
+  <si>
+    <t>LP-058307</t>
+  </si>
+  <si>
+    <t>LP-058306</t>
+  </si>
+  <si>
+    <t>LP-058314</t>
+  </si>
+  <si>
+    <t>LP-058310</t>
+  </si>
+  <si>
+    <t>LP-058311</t>
+  </si>
+  <si>
+    <t>LP-058313</t>
+  </si>
+  <si>
+    <t>LP-058312</t>
+  </si>
+  <si>
+    <t>LP-058425</t>
+  </si>
+  <si>
+    <t>LP-058429</t>
+  </si>
+  <si>
+    <t>LP-058428</t>
+  </si>
+  <si>
+    <t>LP-058321</t>
+  </si>
+  <si>
+    <t>LP-058427</t>
+  </si>
+  <si>
+    <t>LP-058426</t>
+  </si>
+  <si>
+    <t>LP-058423</t>
+  </si>
+  <si>
+    <t>LP-058315</t>
+  </si>
+  <si>
+    <t>LP-058320</t>
+  </si>
+  <si>
+    <t>LP-058302</t>
+  </si>
+  <si>
+    <t>LP-058317</t>
+  </si>
+  <si>
+    <t>LP-058316</t>
+  </si>
+  <si>
+    <t>LP-058318</t>
+  </si>
+  <si>
+    <t>LP-058298</t>
+  </si>
+  <si>
+    <t>LP-058424</t>
+  </si>
+  <si>
+    <t>LP-058293</t>
+  </si>
+  <si>
+    <t>LP-058299</t>
+  </si>
+  <si>
+    <t>LP-058433</t>
+  </si>
+  <si>
+    <t>LP-058451</t>
+  </si>
+  <si>
+    <t>LP-058300</t>
+  </si>
+  <si>
+    <t>LP-058459</t>
+  </si>
+  <si>
+    <t>LP-058460</t>
+  </si>
+  <si>
+    <t>LP-058461</t>
+  </si>
+  <si>
+    <t>LP-058462</t>
+  </si>
+  <si>
+    <t>LP-058463</t>
+  </si>
+  <si>
+    <t>LP-058464</t>
+  </si>
+  <si>
+    <t>LP-058296</t>
+  </si>
+  <si>
+    <t>LP-058295</t>
+  </si>
+  <si>
+    <t>LP-058294</t>
+  </si>
+  <si>
+    <t>LP-058372</t>
+  </si>
+  <si>
+    <t>LP-058319</t>
+  </si>
+  <si>
+    <t>LP-058377</t>
+  </si>
+  <si>
+    <t>LP-058378</t>
+  </si>
+  <si>
+    <t>LP-058506</t>
+  </si>
+  <si>
+    <t>LP-058507</t>
+  </si>
+  <si>
+    <t>LP-058611</t>
+  </si>
+  <si>
+    <t>LP-058612</t>
+  </si>
+  <si>
+    <t>LP-058363</t>
+  </si>
+  <si>
+    <t>LP-058362</t>
+  </si>
+  <si>
+    <t>LP-058455</t>
+  </si>
+  <si>
+    <t>LP-058358</t>
+  </si>
+  <si>
+    <t>LP-058357</t>
+  </si>
+  <si>
+    <t>LP-058360</t>
+  </si>
+  <si>
+    <t>LP-058359</t>
+  </si>
+  <si>
+    <t>LP-058369</t>
+  </si>
+  <si>
+    <t>LP-059552</t>
+  </si>
+  <si>
+    <t>LP-058452</t>
+  </si>
+  <si>
+    <t>LP-058585</t>
+  </si>
+  <si>
+    <t>LP-058483</t>
+  </si>
+  <si>
+    <t>LP-058480</t>
+  </si>
+  <si>
+    <t>LP-058482</t>
+  </si>
+  <si>
+    <t>LP-058468</t>
+  </si>
+  <si>
+    <t>LP-058469</t>
+  </si>
+  <si>
+    <t>LP-058489</t>
+  </si>
+  <si>
+    <t>LP-058488</t>
+  </si>
+  <si>
+    <t>LP-058511</t>
+  </si>
+  <si>
+    <t>LP-058514</t>
+  </si>
+  <si>
+    <t>LP-058472</t>
+  </si>
+  <si>
+    <t>LP-058513</t>
+  </si>
+  <si>
+    <t>LP-058512</t>
+  </si>
+  <si>
+    <t>LP-058524</t>
+  </si>
+  <si>
+    <t>LP-058486</t>
+  </si>
+  <si>
+    <t>LP-058485</t>
+  </si>
+  <si>
+    <t>LP-058484</t>
+  </si>
+  <si>
+    <t>LP-058471</t>
+  </si>
+  <si>
+    <t>LP-058527</t>
+  </si>
+  <si>
+    <t>LP-058487</t>
+  </si>
+  <si>
+    <t>LP-058474</t>
+  </si>
+  <si>
+    <t>LP-058475</t>
+  </si>
+  <si>
+    <t>LP-058476</t>
+  </si>
+  <si>
+    <t>LP-058477</t>
+  </si>
+  <si>
+    <t>LP-058478</t>
+  </si>
+  <si>
+    <t>LP-058479</t>
+  </si>
+  <si>
+    <t>LP-059304</t>
+  </si>
+  <si>
+    <t>LP-058589</t>
+  </si>
+  <si>
+    <t>LP-058530</t>
+  </si>
+  <si>
+    <t>LP-058620</t>
+  </si>
+  <si>
+    <t>LP-058622</t>
+  </si>
+  <si>
+    <t>LP-058623</t>
+  </si>
+  <si>
+    <t>LP-058765</t>
+  </si>
+  <si>
+    <t>LP-058763</t>
+  </si>
+  <si>
+    <t>LP-058764</t>
+  </si>
+  <si>
+    <t>LP-058557</t>
+  </si>
+  <si>
+    <t>LP-058543</t>
+  </si>
+  <si>
+    <t>LP-058563</t>
+  </si>
+  <si>
+    <t>LP-058545</t>
+  </si>
+  <si>
+    <t>LP-058596</t>
+  </si>
+  <si>
+    <t>LP-058614</t>
+  </si>
+  <si>
+    <t>LP-058613</t>
+  </si>
+  <si>
+    <t>LP-058617</t>
+  </si>
+  <si>
+    <t>LP-058619</t>
+  </si>
+  <si>
+    <t>LP-058621</t>
+  </si>
+  <si>
+    <t>LP-058544</t>
+  </si>
+  <si>
+    <t>LP-058541</t>
+  </si>
+  <si>
+    <t>LP-058542</t>
+  </si>
+  <si>
+    <t>LP-058565</t>
+  </si>
+  <si>
+    <t>LP-058564</t>
+  </si>
+  <si>
+    <t>LP-058569</t>
+  </si>
+  <si>
+    <t>LP-058554</t>
+  </si>
+  <si>
+    <t>LP-058561</t>
+  </si>
+  <si>
+    <t>LP-058552</t>
+  </si>
+  <si>
+    <t>LP-058566</t>
+  </si>
+  <si>
+    <t>LP-058567</t>
+  </si>
+  <si>
+    <t>LP-058615</t>
+  </si>
+  <si>
+    <t>LP-058616</t>
+  </si>
+  <si>
+    <t>LP-058618</t>
+  </si>
+  <si>
+    <t>LP-058568</t>
+  </si>
+  <si>
+    <t>LP-058570</t>
+  </si>
+  <si>
+    <t>LP-058559</t>
+  </si>
+  <si>
+    <t>LP-058694</t>
+  </si>
+  <si>
+    <t>LP-058649</t>
+  </si>
+  <si>
+    <t>LP-058685</t>
+  </si>
+  <si>
+    <t>LP-058695</t>
   </si>
 </sst>
 </file>
@@ -464,12 +1100,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C245"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="5.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -488,340 +1124,1951 @@
         <v>3</v>
       </c>
       <c r="B2">
-        <v>3.3</v>
-      </c>
-      <c r="C2" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B3">
-        <v>3.3</v>
-      </c>
-      <c r="C3" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B4">
-        <v>3.3</v>
-      </c>
-      <c r="C4" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B5">
-        <v>3.3</v>
-      </c>
-      <c r="C5" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B6">
-        <v>3.3</v>
-      </c>
-      <c r="C6" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B7">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="C7" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B8">
-        <v>3.3</v>
-      </c>
-      <c r="C8" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B9">
-        <v>3.3</v>
-      </c>
-      <c r="C9" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B10">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="C10" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B11">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="C11" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B12">
-        <v>3.3</v>
-      </c>
-      <c r="C12" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B13">
-        <v>3.3</v>
-      </c>
-      <c r="C13" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B14">
-        <v>6.6</v>
-      </c>
-      <c r="C14" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B15">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="C15" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
         <v>18</v>
       </c>
-      <c r="B16">
-        <v>6.8</v>
-      </c>
-      <c r="C16" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+      <c r="B17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>19</v>
       </c>
-      <c r="B17">
-        <v>3.3</v>
-      </c>
-      <c r="C17" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+      <c r="B18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
         <v>20</v>
       </c>
-      <c r="B18">
-        <v>6.6</v>
-      </c>
-      <c r="C18" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+      <c r="B19">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
         <v>21</v>
       </c>
-      <c r="B19">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="C19" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+      <c r="B20">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>22</v>
       </c>
-      <c r="B20">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="C20" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+      <c r="B21">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
         <v>23</v>
       </c>
-      <c r="B21">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="C21" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+      <c r="B22">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
         <v>24</v>
       </c>
-      <c r="B22">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="C22" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+      <c r="B23">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
         <v>25</v>
       </c>
-      <c r="B23">
-        <v>16.600000000000001</v>
-      </c>
-      <c r="C23" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+      <c r="B24">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
         <v>26</v>
       </c>
-      <c r="B24">
-        <v>12.5</v>
-      </c>
-      <c r="C24" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
+      <c r="B25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
         <v>27</v>
       </c>
-      <c r="B25">
-        <v>12.5</v>
-      </c>
-      <c r="C25" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
+      <c r="B26">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
         <v>28</v>
       </c>
-      <c r="B26">
+      <c r="B27">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>29</v>
+      </c>
+      <c r="B28">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>30</v>
+      </c>
+      <c r="B29">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>31</v>
+      </c>
+      <c r="B30">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>32</v>
+      </c>
+      <c r="B31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
         <v>33</v>
       </c>
-      <c r="C26" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>29</v>
-      </c>
-      <c r="B27">
-        <v>24.9</v>
-      </c>
-      <c r="C27" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>30</v>
-      </c>
-      <c r="B28">
-        <v>8.3000000000000007</v>
-      </c>
-      <c r="C28" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>31</v>
-      </c>
-      <c r="B29">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="C29" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>32</v>
-      </c>
-      <c r="B30">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="C30" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>33</v>
-      </c>
-      <c r="B31">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="C31" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
+      <c r="B32">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
         <v>34</v>
       </c>
-      <c r="B32">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="C32" t="s">
-        <v>4</v>
+      <c r="B33">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>35</v>
+      </c>
+      <c r="B34">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>36</v>
+      </c>
+      <c r="B35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>37</v>
+      </c>
+      <c r="B36">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>38</v>
+      </c>
+      <c r="B37">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>39</v>
+      </c>
+      <c r="B38">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>40</v>
+      </c>
+      <c r="B39">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>41</v>
+      </c>
+      <c r="B40">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>42</v>
+      </c>
+      <c r="B41">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>43</v>
+      </c>
+      <c r="B42">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>44</v>
+      </c>
+      <c r="B43">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>45</v>
+      </c>
+      <c r="B44">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>46</v>
+      </c>
+      <c r="B45">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>47</v>
+      </c>
+      <c r="B46">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>48</v>
+      </c>
+      <c r="B47">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>49</v>
+      </c>
+      <c r="B48">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>50</v>
+      </c>
+      <c r="B49">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>51</v>
+      </c>
+      <c r="B50">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>52</v>
+      </c>
+      <c r="B51">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>53</v>
+      </c>
+      <c r="B52">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>54</v>
+      </c>
+      <c r="B53">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>55</v>
+      </c>
+      <c r="B54">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>56</v>
+      </c>
+      <c r="B55">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>57</v>
+      </c>
+      <c r="B56">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>58</v>
+      </c>
+      <c r="B57">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>59</v>
+      </c>
+      <c r="B58">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>60</v>
+      </c>
+      <c r="B59">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>61</v>
+      </c>
+      <c r="B60">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>62</v>
+      </c>
+      <c r="B61">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>63</v>
+      </c>
+      <c r="B62">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>64</v>
+      </c>
+      <c r="B63">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>65</v>
+      </c>
+      <c r="B64">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>66</v>
+      </c>
+      <c r="B65">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>67</v>
+      </c>
+      <c r="B66">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>68</v>
+      </c>
+      <c r="B67">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>69</v>
+      </c>
+      <c r="B68">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>70</v>
+      </c>
+      <c r="B69">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>71</v>
+      </c>
+      <c r="B70">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>72</v>
+      </c>
+      <c r="B71">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>73</v>
+      </c>
+      <c r="B72">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>74</v>
+      </c>
+      <c r="B73">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>75</v>
+      </c>
+      <c r="B74">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>76</v>
+      </c>
+      <c r="B75">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>77</v>
+      </c>
+      <c r="B76">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>78</v>
+      </c>
+      <c r="B77">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>79</v>
+      </c>
+      <c r="B78">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>80</v>
+      </c>
+      <c r="B79">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>81</v>
+      </c>
+      <c r="B80">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>82</v>
+      </c>
+      <c r="B81">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>83</v>
+      </c>
+      <c r="B82">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>84</v>
+      </c>
+      <c r="B83">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>85</v>
+      </c>
+      <c r="B84">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>86</v>
+      </c>
+      <c r="B85">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>87</v>
+      </c>
+      <c r="B86">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>88</v>
+      </c>
+      <c r="B87">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>89</v>
+      </c>
+      <c r="B88">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>90</v>
+      </c>
+      <c r="B89">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>91</v>
+      </c>
+      <c r="B90">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>92</v>
+      </c>
+      <c r="B91">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>93</v>
+      </c>
+      <c r="B92">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>94</v>
+      </c>
+      <c r="B93">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>95</v>
+      </c>
+      <c r="B94">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>96</v>
+      </c>
+      <c r="B95">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>97</v>
+      </c>
+      <c r="B96">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>98</v>
+      </c>
+      <c r="B97">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>99</v>
+      </c>
+      <c r="B98">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>100</v>
+      </c>
+      <c r="B99">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>101</v>
+      </c>
+      <c r="B100">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>102</v>
+      </c>
+      <c r="B101">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>103</v>
+      </c>
+      <c r="B102">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>104</v>
+      </c>
+      <c r="B103">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>105</v>
+      </c>
+      <c r="B104">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>106</v>
+      </c>
+      <c r="B105">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>107</v>
+      </c>
+      <c r="B106">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>108</v>
+      </c>
+      <c r="B107">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>109</v>
+      </c>
+      <c r="B108">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>110</v>
+      </c>
+      <c r="B109">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>111</v>
+      </c>
+      <c r="B110">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>112</v>
+      </c>
+      <c r="B111">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>113</v>
+      </c>
+      <c r="B112">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>114</v>
+      </c>
+      <c r="B113">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>115</v>
+      </c>
+      <c r="B114">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>116</v>
+      </c>
+      <c r="B115">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>117</v>
+      </c>
+      <c r="B116">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>118</v>
+      </c>
+      <c r="B117">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>119</v>
+      </c>
+      <c r="B118">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>120</v>
+      </c>
+      <c r="B119">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>121</v>
+      </c>
+      <c r="B120">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>122</v>
+      </c>
+      <c r="B121">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>123</v>
+      </c>
+      <c r="B122">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>124</v>
+      </c>
+      <c r="B123">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>125</v>
+      </c>
+      <c r="B124">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>126</v>
+      </c>
+      <c r="B125">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>127</v>
+      </c>
+      <c r="B126">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>128</v>
+      </c>
+      <c r="B127">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>129</v>
+      </c>
+      <c r="B128">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>130</v>
+      </c>
+      <c r="B129">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>131</v>
+      </c>
+      <c r="B130">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>132</v>
+      </c>
+      <c r="B131">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>133</v>
+      </c>
+      <c r="B132">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>134</v>
+      </c>
+      <c r="B133">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>135</v>
+      </c>
+      <c r="B134">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>136</v>
+      </c>
+      <c r="B135">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>137</v>
+      </c>
+      <c r="B136">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>138</v>
+      </c>
+      <c r="B137">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>139</v>
+      </c>
+      <c r="B138">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>140</v>
+      </c>
+      <c r="B139">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>141</v>
+      </c>
+      <c r="B140">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>142</v>
+      </c>
+      <c r="B141">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>143</v>
+      </c>
+      <c r="B142">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>144</v>
+      </c>
+      <c r="B143">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>145</v>
+      </c>
+      <c r="B144">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>146</v>
+      </c>
+      <c r="B145">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>147</v>
+      </c>
+      <c r="B146">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>148</v>
+      </c>
+      <c r="B147">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>149</v>
+      </c>
+      <c r="B148">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>150</v>
+      </c>
+      <c r="B149">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>151</v>
+      </c>
+      <c r="B150">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>152</v>
+      </c>
+      <c r="B151">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>153</v>
+      </c>
+      <c r="B152">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>154</v>
+      </c>
+      <c r="B153">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>155</v>
+      </c>
+      <c r="B154">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>156</v>
+      </c>
+      <c r="B155">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>157</v>
+      </c>
+      <c r="B156">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>158</v>
+      </c>
+      <c r="B157">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>159</v>
+      </c>
+      <c r="B158">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>160</v>
+      </c>
+      <c r="B159">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>161</v>
+      </c>
+      <c r="B160">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>162</v>
+      </c>
+      <c r="B161">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>163</v>
+      </c>
+      <c r="B162">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>164</v>
+      </c>
+      <c r="B163">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>165</v>
+      </c>
+      <c r="B164">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>166</v>
+      </c>
+      <c r="B165">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
+        <v>167</v>
+      </c>
+      <c r="B166">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>168</v>
+      </c>
+      <c r="B167">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>169</v>
+      </c>
+      <c r="B168">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>170</v>
+      </c>
+      <c r="B169">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
+        <v>171</v>
+      </c>
+      <c r="B170">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
+        <v>172</v>
+      </c>
+      <c r="B171">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>173</v>
+      </c>
+      <c r="B172">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
+        <v>174</v>
+      </c>
+      <c r="B173">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
+        <v>175</v>
+      </c>
+      <c r="B174">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
+        <v>176</v>
+      </c>
+      <c r="B175">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
+        <v>177</v>
+      </c>
+      <c r="B176">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A177" t="s">
+        <v>178</v>
+      </c>
+      <c r="B177">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A178" t="s">
+        <v>179</v>
+      </c>
+      <c r="B178">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A179" t="s">
+        <v>180</v>
+      </c>
+      <c r="B179">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A180" t="s">
+        <v>181</v>
+      </c>
+      <c r="B180">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A181" t="s">
+        <v>182</v>
+      </c>
+      <c r="B181">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A182" t="s">
+        <v>183</v>
+      </c>
+      <c r="B182">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
+        <v>184</v>
+      </c>
+      <c r="B183">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A184" t="s">
+        <v>185</v>
+      </c>
+      <c r="B184">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A185" t="s">
+        <v>186</v>
+      </c>
+      <c r="B185">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A186" t="s">
+        <v>187</v>
+      </c>
+      <c r="B186">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A187" t="s">
+        <v>188</v>
+      </c>
+      <c r="B187">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A188" t="s">
+        <v>189</v>
+      </c>
+      <c r="B188">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A189" t="s">
+        <v>190</v>
+      </c>
+      <c r="B189">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A190" t="s">
+        <v>191</v>
+      </c>
+      <c r="B190">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A191" t="s">
+        <v>192</v>
+      </c>
+      <c r="B191">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A192" t="s">
+        <v>193</v>
+      </c>
+      <c r="B192">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A193" t="s">
+        <v>194</v>
+      </c>
+      <c r="B193">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A194" t="s">
+        <v>195</v>
+      </c>
+      <c r="B194">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A195" t="s">
+        <v>196</v>
+      </c>
+      <c r="B195">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A196" t="s">
+        <v>197</v>
+      </c>
+      <c r="B196">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A197" t="s">
+        <v>198</v>
+      </c>
+      <c r="B197">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A198" t="s">
+        <v>199</v>
+      </c>
+      <c r="B198">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A199" t="s">
+        <v>200</v>
+      </c>
+      <c r="B199">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A200" t="s">
+        <v>201</v>
+      </c>
+      <c r="B200">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A201" t="s">
+        <v>202</v>
+      </c>
+      <c r="B201">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A202" t="s">
+        <v>203</v>
+      </c>
+      <c r="B202">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="203" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A203" t="s">
+        <v>204</v>
+      </c>
+      <c r="B203">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A204" t="s">
+        <v>205</v>
+      </c>
+      <c r="B204">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="205" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A205" t="s">
+        <v>206</v>
+      </c>
+      <c r="B205">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="206" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A206" t="s">
+        <v>207</v>
+      </c>
+      <c r="B206">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A207" t="s">
+        <v>208</v>
+      </c>
+      <c r="B207">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A208" t="s">
+        <v>209</v>
+      </c>
+      <c r="B208">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A209" t="s">
+        <v>210</v>
+      </c>
+      <c r="B209">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="210" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A210" t="s">
+        <v>211</v>
+      </c>
+      <c r="B210">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="211" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A211" t="s">
+        <v>212</v>
+      </c>
+      <c r="B211">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A212" t="s">
+        <v>213</v>
+      </c>
+      <c r="B212">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A213" t="s">
+        <v>214</v>
+      </c>
+      <c r="B213">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="214" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A214" t="s">
+        <v>215</v>
+      </c>
+      <c r="B214">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="215" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A215" t="s">
+        <v>216</v>
+      </c>
+      <c r="B215">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="216" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A216" t="s">
+        <v>217</v>
+      </c>
+      <c r="B216">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="217" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A217" t="s">
+        <v>218</v>
+      </c>
+      <c r="B217">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="218" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A218" t="s">
+        <v>219</v>
+      </c>
+      <c r="B218">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="219" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A219" t="s">
+        <v>220</v>
+      </c>
+      <c r="B219">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="220" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A220" t="s">
+        <v>221</v>
+      </c>
+      <c r="B220">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="221" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A221" t="s">
+        <v>222</v>
+      </c>
+      <c r="B221">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="222" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A222" t="s">
+        <v>223</v>
+      </c>
+      <c r="B222">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="223" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A223" t="s">
+        <v>224</v>
+      </c>
+      <c r="B223">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="224" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A224" t="s">
+        <v>225</v>
+      </c>
+      <c r="B224">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="225" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A225" t="s">
+        <v>226</v>
+      </c>
+      <c r="B225">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="226" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A226" t="s">
+        <v>227</v>
+      </c>
+      <c r="B226">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="227" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A227" t="s">
+        <v>228</v>
+      </c>
+      <c r="B227">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="228" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A228" t="s">
+        <v>229</v>
+      </c>
+      <c r="B228">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="229" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A229" t="s">
+        <v>230</v>
+      </c>
+      <c r="B229">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="230" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A230" t="s">
+        <v>231</v>
+      </c>
+      <c r="B230">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="231" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A231" t="s">
+        <v>232</v>
+      </c>
+      <c r="B231">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="232" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A232" t="s">
+        <v>233</v>
+      </c>
+      <c r="B232">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="233" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A233" t="s">
+        <v>234</v>
+      </c>
+      <c r="B233">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="234" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A234" t="s">
+        <v>235</v>
+      </c>
+      <c r="B234">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="235" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A235" t="s">
+        <v>236</v>
+      </c>
+      <c r="B235">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="236" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A236" t="s">
+        <v>237</v>
+      </c>
+      <c r="B236">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="237" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A237" t="s">
+        <v>238</v>
+      </c>
+      <c r="B237">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="238" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A238" t="s">
+        <v>239</v>
+      </c>
+      <c r="B238">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="239" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A239" t="s">
+        <v>240</v>
+      </c>
+      <c r="B239">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="240" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A240" t="s">
+        <v>241</v>
+      </c>
+      <c r="B240">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="241" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A241" t="s">
+        <v>242</v>
+      </c>
+      <c r="B241">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="242" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A242" t="s">
+        <v>243</v>
+      </c>
+      <c r="B242">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="243" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A243" t="s">
+        <v>244</v>
+      </c>
+      <c r="B243">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="244" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A244" t="s">
+        <v>245</v>
+      </c>
+      <c r="B244">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="245" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A245" t="s">
+        <v>246</v>
+      </c>
+      <c r="B245">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
